--- a/光伏配储项目/电价数据/2026/茶寮站.xlsx
+++ b/光伏配储项目/电价数据/2026/茶寮站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.47021</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38459</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.69172</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.5300499999999999</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.5867100000000001</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.47544</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.41581</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.43968</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45685</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.42982</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.4241</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.42248</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.41075</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.39887</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.39825</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38624</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40281</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42538</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41443</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35483</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39295</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38627</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41858</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39346</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42238</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41552</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42559</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41347</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44488</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.49786</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.39894</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.3117799999999999</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.32752</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.35029</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.3728</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.32287</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.34052</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.10862</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.11917</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.16033</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.12741</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.05515</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.09755</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.07054000000000001</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.29811</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.28478</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.04837</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.40087</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.58301</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.14557</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.21569</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.22708</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.2321</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.21632</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.36801</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.32883</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.13511</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.29018</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.30395</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.29072</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.23301</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>-0.03111</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.27683</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.38483</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.53631</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.73165</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.11465</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.39454</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.15728</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.43136</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.4367200000000001</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.6587999999999999</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.87225</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.48053</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.20745</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>0.9653200000000001</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.06548</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.67924</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.28898</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>0.97773</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.4473</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.69129</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.73572</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>0.67924</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.7566799999999999</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.8745000000000001</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.79706</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.7576499999999999</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.5170800000000001</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.48011</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.46829</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41601</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42569</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.78149</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.87426</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.92012</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.49567</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.5162899999999999</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50376</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.50398</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.4862</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.39989</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.46821</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.37845</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.37897</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.38465</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33641</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.36816</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.3536</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.35355</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.36954</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.37148</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.35504</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.37695</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.41344</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.91486</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.7563300000000001</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.8512799999999999</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.46122</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.44475</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.37803</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34771</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.38584</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.42486</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.50843</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.35173</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.33688</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.35671</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.31922</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.31268</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.30723</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.29873</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.32929</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.32909</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.36848</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.49171</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.76115</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.97445</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.32598</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.50613</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.8683200000000001</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.82733</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.48029</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.7037599999999999</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.8918700000000001</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>1.03025</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>1.00239</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.28821</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.34649</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.36616</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.45975</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.5369299999999999</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.4882</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.51473</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.82955</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.61841</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.7432300000000001</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.72734</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.12304</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.94201</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.17004</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.823</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.16845</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.07045</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.2254</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.00184</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.05527</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.6126900000000001</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.94799</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.90427</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.8763099999999999</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.59997</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.92737</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.75788</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.68553</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.45049</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.7805</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.80328</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.44945</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.4285</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.444</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.3335</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37591</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35488</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33466</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.50868</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.48785</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.48776</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.3765</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.44729</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.41439</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.3688</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.38963</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38311</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36342</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.42833</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.44387</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33585</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37042</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39606</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36723</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.36808</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35594</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36145</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35191</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36542</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35841</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38447</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39582</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47306</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.44435</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.4385</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34739</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39467</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35293</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36723</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34744</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.17471</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.17712</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.07102</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.19884</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.07673999999999999</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.2028</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.29394</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.33948</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.32755</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.34115</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.35611</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.37346</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.5321699999999999</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.46885</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.7928200000000001</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.35513</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.56814</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.70825</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.798</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.5216900000000001</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.46772</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.7970499999999999</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.50845</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.62112</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.58656</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.49163</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.42031</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.42674</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.393</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.35313</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.4838</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.50063</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.5686100000000001</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.59217</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.5341699999999999</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.55348</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.26944</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.6173500000000001</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.6430399999999999</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.46518</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.5038899999999999</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.52671</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.58882</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.54476</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.65704</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.29877</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.44651</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.40217</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.44567</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.6117999999999999</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.62129</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.56235</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.7167</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.6211</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.55489</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.47446</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.6085</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.41491</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.45711</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.39758</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34862</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34202</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.52067</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.4952</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.44373</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.39002</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.38983</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.3977</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.36754</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.35939</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.38836</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.38641</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.36224</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.44924</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.36057</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.349</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.36384</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.35804</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.3592</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.33781</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.33534</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.33203</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.33456</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.33182</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.35033</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33909</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.3513</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.38584</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38885</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.34921</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.37546</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.34429</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.39388</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.41665</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.41939</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.35676</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.37558</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.3407</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.31647</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.14149</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.03674</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.31866</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.23088</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.01528</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.27534</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.4084</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.245</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.15588</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.1203</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>-0.03088</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.22773</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.35294</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.32783</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.41021</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.60822</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.33966</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.3295</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.31957</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.34682</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.47634</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.40177</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.40035</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.23506</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.25301</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.26955</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.22525</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.4089</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.4325</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.49813</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.45038</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.46292</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.40011</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.47489</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.51663</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.5354500000000001</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.39885</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.483</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.43354</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.42282</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.50134</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.38903</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.37164</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.37448</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.41719</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.32647</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.3462</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.34667</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.34194</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31916</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32315</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.32048</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.3137</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31816</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.31986</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.31852</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.30141</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.22431</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38227</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.36122</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.32866</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32788</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.33178</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32063</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31896</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31599</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.3186</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31858</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31514</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31655</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.31257</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31395</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.31898</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.31595</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.31047</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.3098399999999999</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31336</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31462</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.32046</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.32144</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.31583</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.32816</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.31943</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.30813</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.28649</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.32637</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.32136</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.27677</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.31875</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.3038</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.29918</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.18347</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.30173</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.23245</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.20473</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.14774</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.27688</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.02718</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.2036</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.26296</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.18352</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.00412</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.00597</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.02643</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.37144</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.36956</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.22104</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.19015</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.20287</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.06042</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.01873</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.02664</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>-0.00011</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>0.26806</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.26551</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.29744</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.29983</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.29595</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.30259</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33572</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33585</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.33448</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.38282</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.38781</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.38285</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.37438</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.35877</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.3947</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39634</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.40567</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46443</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.37289</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39345</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.39614</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.49363</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35372</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35742</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34457</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35449</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.34761</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.36731</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.6225000000000001</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.39019</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.42575</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.40579</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.40348</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.35628</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.35184</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.35442</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.31868</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.3052</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.30599</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.34504</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.31192</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.34422</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.34225</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.33204</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.30031</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.3219</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.3233</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.30947</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.29639</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.30763</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33234</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.3299</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.34214</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.34904</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.32843</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31116</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10261</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04347</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04697999999999999</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.0441</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04478</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.34658</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.0137</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.21322</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.05276</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.28577</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.19727</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.03621</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04335</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04549</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04339</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.03304</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.04529</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04538</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04358</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04422</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.06737</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.06559999999999999</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04984</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.0474</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04790999999999999</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19975</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14272</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28994</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30454</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29282</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29329</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29225</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29678</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34737</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.34843</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34248</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36358</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36258</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33347</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.32748</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.31549</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.3103399999999999</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.39999</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.34758</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.3205</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30704</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29442</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17236</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17092</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15943</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23612</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26883</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28566</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.2707</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29731</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.38522</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.37969</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.42792</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.45594</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41844</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41528</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.38804</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40242</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29929</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15654</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29429</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31343</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31269</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34627</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30067</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38545</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220399999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78528</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49797</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92039</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49456</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9142</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86288</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.29621</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35365</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.8875</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.6316000000000001</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18708</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.8694700000000001</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.59365</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33085</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03291</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.53079</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.79099</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.5395</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.77297</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.77754</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8767699999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87386</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49315</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39868</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.39989</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44994</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20699</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87883</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55102</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62185</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53832</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49769</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45582</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42425</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43714</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.44981</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38817</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.41974</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.34948</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.39923</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36401</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38426</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.412</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43018</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34182</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.38859</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.34825</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.33731</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.33066</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.34265</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.39401</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34745</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45003</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.35031</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.39646</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.3922</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.57287</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.42317</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.59046</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.7220299999999999</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.87834</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.46767</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.40537</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.5668</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.44278</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.8474700000000001</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.5999099999999999</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.8565700000000001</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.87499</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.34338</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.42918</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.66351</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.33162</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.30431</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.2973</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.65743</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.59284</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.34932</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31055</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.35495</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33159</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32079</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.40648</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.33575</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31753</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.31954</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.3191000000000001</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31965</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.34002</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.31207</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.31952</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.30261</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29588</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.3117799999999999</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.31177</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.31144</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.30158</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.30534</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.30976</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.31773</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.31713</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.32025</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.35133</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.33571</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.33726</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.33516</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.32745</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.33306</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.33119</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.39932</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.40172</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.43812</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.40387</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.38298</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.36658</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.35046</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.9162899999999999</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.35522</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.4549</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.41531</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.4018</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.45197</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.37398</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.40019</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.35681</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.36067</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.34523</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.34392</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.34083</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.32763</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35394</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.34124</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32027</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.3892</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.48149</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.35181</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.37862</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.33889</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.34555</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.34948</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.36337</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35218</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.35697</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31238</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31153</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.32907</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.33428</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.33476</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.34548</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.31383</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.31191</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.28966</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31258</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.30078</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.29915</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.17738</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30426</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30837</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.33622</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.33236</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.34659</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.30907</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.27307</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.19848</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.30667</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.2988</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.32161</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.28259</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.31056</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.31099</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.35091</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.35989</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.31212</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.3073</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.31586</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.31586</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.3334</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.3135</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.30573</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.29846</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.30551</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.31515</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.31118</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.28944</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.34316</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.25489</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.34436</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.31767</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.33165</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.33344</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27567</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.34377</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.3252</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.33521</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.30624</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.34454</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.33314</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.37786</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.3457</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.42846</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.35324</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.33856</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.42205</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.34898</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44557</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.33318</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.41092</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35548</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.39146</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.38971</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.56612</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.33623</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.8795299999999999</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.45137</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.15157</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.69423</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.78485</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.64574</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.5444600000000001</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.42683</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.44605</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.49625</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.43587</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.42772</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41084</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.40929</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.41468</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.48261</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.40938</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43035</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.40159</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43065</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.38753</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.4145</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.43478</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39279</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.42027</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.42032</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.40939</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.4103</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.3895</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.40952</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.39503</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.3913</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.49125</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.36006</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.32755</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.29249</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.35656</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.36269</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.30831</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.33814</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.30604</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.31314</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.30166</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.5381</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.36064</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.26973</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.24915</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.30514</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.15534</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.27663</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.27553</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>-0.01168</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.33769</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30117</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.26096</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.25443</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.30384</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.28242</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.27147</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.27234</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.29066</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.30765</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.31223</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.3214</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.32451</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.31346</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.33486</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.33565</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.39604</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.39282</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.34771</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.35683</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.33683</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.32906</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.36439</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.33897</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.354</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.36024</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.35869</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.5571799999999999</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.4485</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.8173899999999999</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.45019</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.41595</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.37119</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.44985</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.37797</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.36249</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.3292</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.33244</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32453</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.31598</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.40659</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.33331</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.32031</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33178</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.31073</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.31423</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.31006</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.30992</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.30547</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.30075</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.31851</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.31696</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.31526</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.31133</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.30143</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.30142</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.30533</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.32023</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.3068</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.28207</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.30486</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.37047</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.28691</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.33351</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.37759</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.35434</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.34032</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33431</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.34176</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.32499</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.31651</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.31543</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.26146</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.3285</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.29317</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.27302</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.29249</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.28661</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.22718</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.15939</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.16774</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.28399</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.17682</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.15734</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.15992</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.26434</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.16871</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.25281</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.16479</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.25914</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.2844100000000001</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.17311</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.14174</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.13494</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.14159</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.14632</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.21282</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.16141</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.27933</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.31513</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.33097</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.31978</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.35133</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31833</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.35194</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.34246</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.36222</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.33873</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.37194</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.34232</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.38935</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.35352</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.37544</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.43387</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.38888</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.38108</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.39039</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.38701</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.4371</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.42466</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.4245</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.42918</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44094</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.39857</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.38663</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39399</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.38785</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.35153</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.35227</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.33749</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34185</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.33397</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.5157200000000001</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.38564</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.45258</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.41189</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.4045899999999999</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.36302</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.37299</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.37157</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.38385</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.3765</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.36705</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.37308</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.35451</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.3827</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.36355</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.37217</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.34479</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.34208</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.34961</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.33985</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.33555</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.34023</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.33555</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.34521</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.43542</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.3629</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.37252</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.3542</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.3363</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.33547</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.3365</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32466</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.33803</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.34481</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.35814</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.29627</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.31287</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31491</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.30902</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.29331</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.27804</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.27012</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.23832</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.11215</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.30202</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.21793</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.24738</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.27506</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30087</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.30129</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31803</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31838</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.31558</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.36517</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31348</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.33513</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.29653</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.24038</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.31602</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.30567</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.3229</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.29232</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.28265</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.43666</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.3193</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.32388</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.3209</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.33751</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.27478</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.19336</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.37869</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.34437</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.3448</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.34502</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.32463</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.33579</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.34953</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.30403</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.16599</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.37964</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.37649</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.3463</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.3465</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.34421</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.3836</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.34399</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.34718</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.35385</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.36454</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.35102</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.371</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.37348</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.37781</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.34536</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.35466</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.33791</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36003</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.48323</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.36748</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.4952</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.3733399999999999</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.34767</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.36169</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.35309</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.34498</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.33658</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.3421</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.34069</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.34438</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.34359</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.34387</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.33825</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.33711</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.3398</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33526</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.33356</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.33658</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33224</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.3359</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.33854</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.34444</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.37107</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.3769</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.37486</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.36854</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.34502</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.3367</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.39879</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.38261</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.46341</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.86412</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.4222</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.5539299999999999</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.25979</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.50413</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.48733</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.25248</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.45715</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.38711</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.26029</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.29786</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.41067</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.59084</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.26287</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.08904000000000001</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.7552300000000001</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.11172</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.45988</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.03523</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.18906</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.80641</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.19354</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.17957</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.17441</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.18408</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.2134</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.41033</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.30088</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.2498</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.12206</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.37343</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.15117</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.31389</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.18467</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.32379</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.28827</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.37832</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.3007</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.29866</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.31113</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.42556</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.16868</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.40684</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.38876</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.66277</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.33474</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.7095399999999999</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.64798</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.54674</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.37149</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.5067699999999999</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.24497</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.37465</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.35305</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.33475</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.33143</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.33963</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.3216</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.34557</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.22043</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.32637</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32002</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.41404</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.41539</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.34441</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.32861</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.34213</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.36165</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.33024</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.28517</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.31536</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.33665</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32282</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.32338</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.32419</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.32148</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.29418</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.31979</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.31663</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.30854</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.31198</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31684</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.32002</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.31989</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.31636</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.32106</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.33212</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.33551</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.33197</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.31707</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33655</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.32138</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.33644</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.35269</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.37658</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.37573</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.3316</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.19259</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.37365</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.3455299999999999</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.31276</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.34605</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.33681</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.32198</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.33975</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.33956</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.31346</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.3319</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28046</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.33044</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.314</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.31757</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.32256</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32497</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33139</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.33501</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.32187</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.32286</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.31402</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.31547</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.31645</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.22265</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.34451</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.18728</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.0442</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.2037</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.33865</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.33688</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.33522</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.35042</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.34635</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.34529</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.3449700000000001</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.31179</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.32322</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.28522</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.3424</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.36325</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.36169</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.3536</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.35375</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.35479</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.35992</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.35726</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.37477</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.37597</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.36855</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.38336</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35185</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.36962</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.36238</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.34514</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.33117</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.33772</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.3466</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.33482</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.34737</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.34636</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.34738</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.34834</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.34781</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.34701</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.3425</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34637</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34322</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.32173</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34401</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.34223</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.343</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33063</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.33655</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.33701</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.33415</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.36057</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32135</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.33271</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.33655</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.34281</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.33147</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.33289</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34201</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.33066</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.34342</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.34337</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33325</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.33409</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.32283</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.3420299999999999</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.33564</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.32592</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.33136</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.30484</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.32289</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32547</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.32724</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.32412</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.3167</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.32542</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.31634</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31674</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.32653</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32348</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32868</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31762</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.36977</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32128</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31953</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.21737</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.08940000000000001</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.30036</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.27803</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.30575</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.30704</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.29971</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.28863</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.34458</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.33557</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34008</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.35501</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.28107</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35079</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.3566</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.35985</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.34672</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.35298</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.33656</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.35444</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.35574</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.35474</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.34568</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.37674</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.36313</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.37117</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.37853</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.4171</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.39581</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.3731</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.37277</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.65378</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.62702</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.44105</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.24557</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.43372</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.28096</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.34734</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.26861</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35621</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.33663</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.33968</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32206</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.40805</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37319</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.36596</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.35895</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.35609</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35576</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.35893</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.35502</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.35566</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.35588</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.34974</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.35689</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.35537</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35303</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.34898</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35434</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.35638</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35671</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.34457</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.36182</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35568</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35342</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.35698</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.35698</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.3718</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36278</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.37679</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35347</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35338</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.34809</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.34878</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35482</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34646</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.3277</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.32432</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.33169</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.32364</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.26929</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.16169</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.30126</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.28896</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.28966</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.2112</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.26346</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.31856</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.32043</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.28435</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.22571</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.2618</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.28863</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.28121</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.30297</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.29323</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.3056</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.31289</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.37674</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.30852</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.30594</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.30381</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.34356</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.32057</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.33697</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.33053</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.33276</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.35155</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.33757</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.31707</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33327</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.36374</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.34829</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.35634</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.35288</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.42384</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.38445</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.42791</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.6501399999999999</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.6079600000000001</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.6185</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.47862</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.8158</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.4737</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.7832899999999999</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.44529</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.49471</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.40613</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.3799</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.35554</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.46193</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.41957</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.40925</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.37293</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.37192</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36237</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.35567</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34575</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.47316</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.55432</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.4956</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.65544</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.40692</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.40728</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.39429</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.40045</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.39912</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.40643</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.39079</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.39154</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.40256</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.40064</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.38735</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.38484</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.4079</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.37998</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.40608</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.38214</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.38863</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.39025</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.4023</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.38915</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.43348</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.43377</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.53377</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.48131</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.43666</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.47745</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.43486</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.34866</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.21669</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.3448</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.26387</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.30047</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.26738</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.38039</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.43128</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.37201</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.35191</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.36051</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.35882</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.3574</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.37459</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.31269</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.26149</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.29259</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.2837</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.36293</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.6123</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.24411</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>1.03767</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.33673</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.32713</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.32773</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.32999</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.24383</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.33935</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.31201</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.33476</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.35271</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.34167</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.36512</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.3557</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.36326</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.36797</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.37837</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.34915</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.37423</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.33514</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.40289</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.42503</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.47585</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.43518</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.49282</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.49331</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.53038</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.66352</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.7862100000000001</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.87861</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.6309600000000001</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.76115</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.61729</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.44496</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.78442</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.76773</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.6207</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.6693300000000001</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.35387</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.42029</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.46578</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.46111</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.45409</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.40754</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.5294800000000001</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.41707</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.42944</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.44176</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.43128</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.4212</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.43235</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.41294</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.39025</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.43577</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.3862</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.393</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.39566</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.37803</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.37132</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.366</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.35698</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35378</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36276</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.33742</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.36133</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.35227</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35665</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36276</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.37492</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.37915</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.37633</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.35858</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.35819</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35195</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.3762799999999999</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.39763</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.36503</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.38447</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.39612</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.38763</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38343</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35143</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.36507</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.34259</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.33649</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.34378</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.37305</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.34834</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.31286</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.31276</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.32999</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.31911</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.34319</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.3311</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.41679</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.36774</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.42748</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.16774</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.31575</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.13224</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.20401</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29806</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32227</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.34845</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.34336</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.34398</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.34532</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.36539</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.38581</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.38769</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.34311</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.3971</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.35503</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.42907</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.41427</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.43723</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.40491</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.40361</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.36909</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.37343</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.39175</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.39561</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.33678</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.35656</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37285</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.38405</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.35698</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.37048</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35854</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.3881</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.36046</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.36668</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.33967</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.37447</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.36028</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.34964</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.31479</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.48063</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.25654</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.39003</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.37673</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.2693</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.36275</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.33146</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.33936</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.34674</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.32125</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.31824</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.33136</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.32054</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.33113</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.34826</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.33049</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.30432</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.31327</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.3215</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.32536</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.31708</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.32185</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.32662</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.29574</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.33139</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.29469</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.29214</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.35049</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.30385</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.30018</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.3108399999999999</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.28805</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.34681</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.3197</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.31058</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.30963</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.20734</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.28479</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.23731</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.27935</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.25536</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.25228</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.11858</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.32216</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.30895</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.29572</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.25379</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.03890999999999999</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.29106</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.2804</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.18145</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.18853</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.30879</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.31292</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.3084</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.24118</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.26316</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.2604</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.2372</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.27637</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28502</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.28074</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.32699</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.33075</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.32271</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.34679</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.3429</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.34957</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.37135</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.34822</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.34507</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.31442</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.36945</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.38945</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.32838</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.30684</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.36592</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.34948</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.36755</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.3446</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.35873</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.3789</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.35375</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.3129</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.35163</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.36077</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.3283</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.35165</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.34839</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.35995</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.33822</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.32894</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.34034</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.32899</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.33729</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.31174</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.26769</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.3349</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.33474</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.33725</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.33044</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.30356</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.30893</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.30428</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.31219</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.27547</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.29838</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.3041</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.30075</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.28049</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.27631</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.27761</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.2776</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.27397</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.27397</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.27615</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.29408</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.27196</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.27397</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.27432</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.29647</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.27648</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.27624</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.33033</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.28275</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.18902</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.27035</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.23691</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.01539</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00043</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-0.00011</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04958</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.14706</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.02143</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03957</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.01524</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04289</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.04078</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04859</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04824000000000001</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02446</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02926</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.04886</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.0494</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.27512</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04965</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.0493</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.03793</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.01802</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04964</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.03604</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.20225</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.26548</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.28905</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.2795</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.30847</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.31145</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.27934</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.31484</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.33404</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.34769</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.3405899999999999</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.34582</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.31469</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.3178</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.35632</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.34573</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.35033</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.3441</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.34222</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.35025</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.34515</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.37254</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.43526</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.35822</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.37539</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.35388</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.3499</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.34933</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.34237</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.35124</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.31859</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.34114</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.7906299999999999</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.67944</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.3997</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.48344</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.41008</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.43037</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.4448</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.3719</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.36288</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.34283</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.32992</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.34295</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.33825</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.33758</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.32788</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.30632</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.35325</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.28325</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.32451</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.31027</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.3410899999999999</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.30765</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.32686</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.34048</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.36591</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.44023</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.3813</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.35051</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.34977</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.3079</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.38704</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.7802100000000001</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.9079299999999999</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.88103</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.85322</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.32642</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.3863</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.11952</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.25017</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.29956</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.3104</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.30059</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.30268</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.26723</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.30038</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.35438</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>-0.005889999999999999</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.26214</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.27305</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.00245</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.27544</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.0014</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.31251</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.31763</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.29496</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.06019</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.28869</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.29947</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.29131</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.3035</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25432</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29171</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.47162</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.31933</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.32641</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.3476</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.38177</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.39483</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.3479</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.37375</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.36337</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.39644</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>1.59289</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.8194400000000001</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.80483</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.80779</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>1.40077</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.9792799999999999</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.80471</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.85768</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.8357899999999999</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.84272</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.84092</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.8452000000000001</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.94229</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.80016</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.83174</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.8021200000000001</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.37085</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.36036</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.37535</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.37104</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.37088</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.48342</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.64483</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.75552</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.60466</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.49662</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.48158</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.41686</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.4080299999999999</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.38399</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.38703</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.37842</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.34256</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.34825</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.33696</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.3332</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.49937</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.33723</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.33583</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.33069</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.32614</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.33069</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.32506</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.36794</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.36181</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.38367</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.48099</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.49798</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.38318</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.40167</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.32499</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.33309</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.33947</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.44251</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.37949</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.48108</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.3707</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.41965</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.41345</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.36396</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.35947</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.34366</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.40702</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.34751</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.3127799999999999</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.32432</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.33085</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.31138</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.262</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.3141600000000001</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.30528</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30539</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32681</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.32294</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.32056</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.351</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.31858</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.32758</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31534</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.31778</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.32207</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.33792</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.34237</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32956</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.33158</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32546</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.34566</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.34799</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.34444</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.3562</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.34519</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.35403</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.33361</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.36432</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.40207</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.39424</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.38074</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.34766</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.37945</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.37585</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.42916</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.47862</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.80174</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.41887</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.6398400000000001</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.48029</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.3871</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.43972</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.4319</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.40649</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.50643</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.36257</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.36879</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.35022</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.3536</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.34911</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.43348</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.43904</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.42106</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.40606</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.39592</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.39151</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.38817</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.36535</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.36976</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.36191</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.36165</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.35073</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.35707</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.35381</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.34628</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.36209</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.34477</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.34392</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.33831</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.33987</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.34115</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.34123</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.35238</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.34389</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.36101</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.35337</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.36172</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35305</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.36349</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.43057</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.37835</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.3672</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.6047100000000001</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.8050900000000001</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.58673</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.49997</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.5908600000000001</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.47328</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.36565</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.3592</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.35037</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.34955</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.35936</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.33761</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.35706</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.39063</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.35258</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.30466</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.31718</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.29602</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.31045</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.2705</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.31763</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.34255</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.33283</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32544</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.32306</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.28841</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.32797</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.32858</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.33307</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.3224</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.34848</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.3471</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.29542</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.35217</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.47391</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.11363</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.76754</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.33731</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.3358</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.49448</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.05004</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.76695</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.36262</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.74527</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.5972000000000001</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.48337</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.48247</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.3774</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.31053</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.31569</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.33796</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.35706</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.35737</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.44105</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.3909</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.36359</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.39227</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.37238</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.2432</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.36502</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.35295</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.3611</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.3427</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.46695</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.39216</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.39047</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.38193</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.37612</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.35417</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.36698</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37019</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37071</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.36912</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36043</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.35954</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.35507</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.35302</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35433</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.35396</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.34821</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32364</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.34874</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.34292</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.34086</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.33963</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.3454</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.35101</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.36082</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.38671</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.36465</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.36119</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.35189</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.35573</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.35431</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.35602</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.38548</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.3912</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.37014</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.35386</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.4349</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.3799</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.36705</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.37832</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.35998</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.31053</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.36362</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.15694</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.36348</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.31664</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.34175</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.2926</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.26565</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.306</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.32669</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.28038</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31622</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33663</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.34369</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32532</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33351</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.3417</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.33818</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.32486</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34421</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.3444700000000001</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.37612</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.37082</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.37639</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.3492</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.38144</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.40137</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.37829</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.38131</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.42281</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.41991</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.5114300000000001</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.52626</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.17139</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.22653</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.7379</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.4487</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.45291</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.44609</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.64664</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.4853</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.66201</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.73748</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.91139</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.8056</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.73842</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.8105800000000001</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.33543</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.39428</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.38048</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.36712</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.37066</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.36056</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.36543</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.30484</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.36428</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.36419</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.35805</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.35437</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.34481</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.33795</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.34953</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.3428</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.3413</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.34793</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.3314</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.3829</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.34774</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.33722</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.34972</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.34579</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.29692</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.33496</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.33786</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.34307</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.33922</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.33821</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.35118</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.35839</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.35255</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.38035</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.38045</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.35811</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.34984</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.34721</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.34545</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.37751</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.33907</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.35605</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.35675</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.33783</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.34937</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.31836</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>-0.04075</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.14482</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.25078</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.06013</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.20902</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.28717</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>-0.02112</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.07428</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.11865</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.25509</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.22469</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.00409</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.34684</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.09043999999999999</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.25175</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.09486</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.0109</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.06625</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.2719</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.34838</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.34365</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.29889</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.34853</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.36719</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.33356</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.25757</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.26273</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.34387</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.37115</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.37508</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.32424</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.23531</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.32619</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.34644</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.29377</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.37049</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.29289</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.45366</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.40221</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.20994</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.35139</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.38288</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.35136</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.28355</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.40722</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.36048</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.41898</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.37627</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.36556</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.32888</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.35077</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.37299</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34272</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.9384</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.30837</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.56747</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.47578</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.30495</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.37299</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.45045</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.37956</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.39366</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.37847</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.37586</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.37761</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.37443</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.37061</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.37708</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.37462</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.3737799999999999</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.37413</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.36959</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.36465</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.37103</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.36847</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.36808</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.36513</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.35671</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.36465</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.35932</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.3781</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.36297</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.35002</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.3541</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.35906</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.36647</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.36756</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.36107</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.34469</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.38012</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.36661</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.3607</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.36254</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.17583</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.32899</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.34496</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.34868</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.44007</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.32287</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.33941</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.30413</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.2817</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.33631</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.33598</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.31538</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.34288</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.24212</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.41121</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.31417</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.3231</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.33471</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.35013</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32335</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.35568</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.35822</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.33077</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.35677</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.34585</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.35432</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.38694</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.36839</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.42915</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.41018</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.39918</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.35958</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.36867</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.38732</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.36744</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.33688</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.32046</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.35207</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.34571</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.36706</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.3896</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.36072</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.3884</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.257</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.24885</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.25305</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.34161</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.36759</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.30914</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.32888</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.32624</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.36227</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.36211</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.36286</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.36382</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.34825</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.42534</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.38968</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.38179</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.37158</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.38089</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.37952</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.37387</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.37625</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.3696</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.37442</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.36503</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.36579</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.36658</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.36264</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.3536</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.36347</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.36427</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.36455</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.36004</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.36003</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.36097</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.36031</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.36294</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.35497</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.34589</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.361</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.35423</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.35508</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.31488</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.31755</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.31945</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.17565</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.30582</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.29473</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.31082</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.14533</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.19803</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.14167</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.29041</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04467</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.12075</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.32889</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.22484</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.26357</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.14985</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.14345</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.28694</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.19463</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.30283</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.22618</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.26318</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.15368</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.35651</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.3078</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.15378</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.31074</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.30004</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.19735</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.14384</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.21999</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.32528</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.32282</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.2829100000000001</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.3083</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.34765</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.35295</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.36719</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.3426</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.34494</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.34843</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.38651</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.26704</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.30634</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.33131</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.21496</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.36411</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.36199</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.37178</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.32557</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.36461</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.39326</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.38332</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.36131</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.39887</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.46552</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.39344</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.36932</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.37242</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.37887</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.35869</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.3814</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.38788</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.38835</v>
       </c>
     </row>
   </sheetData>
